--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jun-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jun-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>641.7</v>
+        <v>28955.72</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>419.328</v>
+        <v>18921.53</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>625.1</v>
+        <v>28206.67</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>483.6</v>
+        <v>21821.7</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>334.6994</v>
+        <v>15102.79</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>9556.715</v>
+        <v>431231.97</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>643.3266</v>
+        <v>29029.12</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>382.9182</v>
+        <v>17278.59</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>194</v>
+        <v>8753.950000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>506.8686</v>
+        <v>22871.66</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>5620.16</v>
+        <v>253601.02</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>313.4432</v>
+        <v>14143.64</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1400.7276</v>
+        <v>63205.66</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>855.048</v>
+        <v>38582.72</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>667.9632</v>
+        <v>30140.81</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>434.826</v>
+        <v>19620.85</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>875.104</v>
+        <v>39487.71</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>364.56</v>
+        <v>16450.21</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>719.355</v>
+        <v>32459.78</v>
       </c>
     </row>
     <row r="21">
@@ -1728,11 +1728,11 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>9253668</v>
+        <v>10243.33</v>
       </c>
     </row>
     <row r="22">
@@ -1789,11 +1789,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>706.8</v>
+        <v>31893.26</v>
       </c>
     </row>
     <row r="23">
@@ -1850,11 +1850,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>642.8067</v>
+        <v>29005.66</v>
       </c>
     </row>
     <row r="24">
@@ -1911,11 +1911,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>819.9924999999999</v>
+        <v>37000.89</v>
       </c>
     </row>
     <row r="25">
@@ -1972,11 +1972,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>247.4858</v>
+        <v>11167.41</v>
       </c>
     </row>
     <row r="26">
@@ -2033,11 +2033,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1175.04</v>
+        <v>53021.86</v>
       </c>
     </row>
     <row r="27">
@@ -2094,11 +2094,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>238.62</v>
+        <v>10767.36</v>
       </c>
     </row>
     <row r="28">
@@ -2155,11 +2155,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>265.58</v>
+        <v>11983.89</v>
       </c>
     </row>
     <row r="29">
@@ -2216,11 +2216,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>919.08</v>
+        <v>41472.06</v>
       </c>
     </row>
     <row r="30">
@@ -2277,11 +2277,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>339.45</v>
+        <v>15317.16</v>
       </c>
     </row>
     <row r="31">
@@ -2338,11 +2338,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1978.3678</v>
+        <v>89270.78</v>
       </c>
     </row>
     <row r="32">
@@ -2399,11 +2399,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>332.01</v>
+        <v>14981.44</v>
       </c>
     </row>
     <row r="33">
@@ -2460,11 +2460,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>693.72</v>
+        <v>31303.04</v>
       </c>
     </row>
     <row r="34">
@@ -2521,11 +2521,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1509.72</v>
+        <v>68123.78</v>
       </c>
     </row>
     <row r="35">
@@ -2582,11 +2582,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>369.303</v>
+        <v>16664.23</v>
       </c>
     </row>
     <row r="36">
@@ -2643,11 +2643,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>873.6504</v>
+        <v>39422.12</v>
       </c>
     </row>
     <row r="37">
@@ -2704,11 +2704,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>725.4</v>
+        <v>32732.55</v>
       </c>
     </row>
     <row r="38">
@@ -2765,11 +2765,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>713.2821</v>
+        <v>32185.75</v>
       </c>
     </row>
     <row r="39">
@@ -2826,11 +2826,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>832.6668</v>
+        <v>37572.8</v>
       </c>
     </row>
     <row r="40">
@@ -2887,11 +2887,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>870.09</v>
+        <v>39261.46</v>
       </c>
     </row>
     <row r="41">
@@ -2948,11 +2948,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>197.4</v>
+        <v>8907.370000000001</v>
       </c>
     </row>
     <row r="42">
@@ -3009,11 +3009,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>9258.5304</v>
+        <v>417776.85</v>
       </c>
     </row>
     <row r="43">
@@ -3070,11 +3070,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1884.61</v>
+        <v>85040.11</v>
       </c>
     </row>
     <row r="44">
@@ -3131,11 +3131,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2961.1008</v>
+        <v>133615.09</v>
       </c>
     </row>
     <row r="45">
@@ -3192,11 +3192,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>418.5</v>
+        <v>18884.16</v>
       </c>
     </row>
     <row r="46">
@@ -3253,11 +3253,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>649.9</v>
+        <v>29325.73</v>
       </c>
     </row>
   </sheetData>
